--- a/tools/levels/out/關卡設定表.xlsx
+++ b/tools/levels/out/關卡設定表.xlsx
@@ -176,7 +176,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">隨機</t>
+          <t xml:space="preserve">ball</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -231,15 +231,40 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t xml:space="preserve">.1.1..1..</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.1.1..1..</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.1.1..1..</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t xml:space="preserve">.111..1..</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t xml:space="preserve">.1.1..1..</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.1.1..1..</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.1.1..1..</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t xml:space="preserve">.1.1.111.</t>
         </is>
@@ -264,7 +289,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">隨機</t>
+          <t xml:space="preserve">bomb</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -309,37 +334,52 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.12...11.</t>
+          <t xml:space="preserve">..2...1..</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111.1111</t>
+          <t xml:space="preserve">1111.111.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121112111</t>
+          <t xml:space="preserve">12111211.</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1111111.</t>
+          <t xml:space="preserve">21111111.</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t xml:space="preserve">..21111..</t>
+          <t xml:space="preserve">22211112.</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t xml:space="preserve">...1G1...</t>
+          <t xml:space="preserve">.221G122.</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t xml:space="preserve">....G....</t>
+          <t xml:space="preserve">..22222..</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...212...</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">....1....</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">....1....</t>
         </is>
       </c>
     </row>
@@ -417,27 +457,42 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21B111B11</t>
+          <t xml:space="preserve">25555554.</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t xml:space="preserve">111111121</t>
+          <t xml:space="preserve">15G55G54.</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.111.G1</t>
+          <t xml:space="preserve">15555554.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t xml:space="preserve">.11...11.</t>
+          <t xml:space="preserve">.4444444.</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t xml:space="preserve">..111G1..</t>
+          <t xml:space="preserve">.4333..4.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.3....33.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">..33331..</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...111...</t>
         </is>
       </c>
     </row>
@@ -465,7 +520,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">a_four</t>
+          <t xml:space="preserve">a_fish_4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -500,42 +555,57 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t xml:space="preserve">.........</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t xml:space="preserve">....2....</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t xml:space="preserve">...222...</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t xml:space="preserve">..22222..</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.2222222.</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t xml:space="preserve">...2G2...</t>
+          <t xml:space="preserve">..12G21..</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t xml:space="preserve">...1G1...</t>
+          <t xml:space="preserve">1111G111.</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t xml:space="preserve">111111111</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...112...</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...333...</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t xml:space="preserve">...111...</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...112...</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...111...</t>
         </is>
       </c>
     </row>
@@ -563,7 +633,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">a_fish</t>
+          <t xml:space="preserve">c_fish_5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -634,6 +704,21 @@
       <c r="Z6" t="inlineStr">
         <is>
           <t xml:space="preserve">111GBG111</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.........</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">545555.55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">444444444</t>
         </is>
       </c>
     </row>
@@ -661,7 +746,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">a_tri</t>
+          <t xml:space="preserve">d_classic</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -673,10 +758,10 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -727,6 +812,26 @@
       <c r="Y7" t="inlineStr">
         <is>
           <t xml:space="preserve">1111G111G</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111111114</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">414441411</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">444444111</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111111111</t>
         </is>
       </c>
     </row>
@@ -759,7 +864,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">M</t>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="H8">
@@ -818,6 +923,26 @@
         </is>
       </c>
       <c r="Y8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.2.2.2.2.</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">..5.5.5..</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...4.4.4.</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">..3.3.3..</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t xml:space="preserve">.2.2.2.2.</t>
         </is>
@@ -945,17 +1070,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">M</t>
+          <t xml:space="preserve">L</t>
         </is>
       </c>
       <c r="H10">
         <v>12</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1045,10 +1170,10 @@
         <v>12</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1087,14 +1212,14 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t xml:space="preserve">.........</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t xml:space="preserve">....X....</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.........</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t xml:space="preserve">.........</t>
@@ -1102,12 +1227,32 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.3.3.G.</t>
+          <t xml:space="preserve">.1.3.3...</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.2.2.1G</t>
+          <t xml:space="preserve">B2.2.2.1B</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">....G....</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333333333</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">444444444</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.3333333.</t>
         </is>
       </c>
     </row>

--- a/tools/levels/out/關卡設定表.xlsx
+++ b/tools/levels/out/關卡設定表.xlsx
@@ -751,7 +751,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M</t>
+          <t xml:space="preserve">L</t>
         </is>
       </c>
       <c r="H7">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">L</t>
+          <t xml:space="preserve">M</t>
         </is>
       </c>
       <c r="H10">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve">L</t>
         </is>
       </c>
       <c r="H11">

--- a/tools/levels/out/關卡設定表.xlsx
+++ b/tools/levels/out/關卡設定表.xlsx
@@ -419,14 +419,14 @@
         <v>12</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="L4">
@@ -532,14 +532,14 @@
         <v>12</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="L5">
@@ -645,14 +645,14 @@
         <v>12</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="L6">
@@ -660,7 +660,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="Q6">
@@ -765,7 +765,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="L7">
@@ -773,7 +773,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="Q7">
@@ -871,14 +871,14 @@
         <v>12</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="L8">
@@ -886,7 +886,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="Q8">
@@ -984,14 +984,14 @@
         <v>12</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="L9">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="Q9">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="L10">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="Q10">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="L11">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">否</t>
         </is>
       </c>
       <c r="N11">

--- a/tools/levels/out/關卡設定表.xlsx
+++ b/tools/levels/out/關卡設定表.xlsx
@@ -422,7 +422,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>3</v>
       </c>
       <c r="J7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>3</v>
       </c>
       <c r="J10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>3</v>
       </c>
       <c r="J11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>8</v>
       </c>
       <c r="J14">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>8</v>
       </c>
       <c r="J16">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>8</v>
       </c>
       <c r="J17">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>8</v>
       </c>
       <c r="J19">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>8</v>
       </c>
       <c r="J20">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>8</v>
       </c>
       <c r="J21">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>

--- a/tools/levels/out/關卡設定表.xlsx
+++ b/tools/levels/out/關卡設定表.xlsx
@@ -171,7 +171,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HI</t>
+          <t xml:space="preserve">第一塊</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -212,7 +212,7 @@
         </is>
       </c>
       <c r="Q2">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -221,52 +221,52 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.1.111.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.1..1..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.1..1..</t>
+          <t xml:space="preserve">....1....</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.1..1..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.1..1..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.111..1..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.1..1..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.1..1..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.1..1..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1.1.111.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
     </row>
@@ -284,12 +284,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">愛心</t>
+          <t xml:space="preserve">道具磚</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bomb</t>
+          <t xml:space="preserve">ball</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c r="Q3">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -334,52 +334,52 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">..2...1..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111.111.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111211.</t>
+          <t xml:space="preserve">...1G1...</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21111111.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22211112.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.221G122.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t xml:space="preserve">..22222..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t xml:space="preserve">...212...</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t xml:space="preserve">....1....</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t xml:space="preserve">....1....</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
     </row>
@@ -397,12 +397,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">笑臉</t>
+          <t xml:space="preserve">加速帶</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">隨機</t>
+          <t xml:space="preserve">bomb,ball</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="Q4">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -447,52 +447,52 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">..11111..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t xml:space="preserve">.1111111.</t>
+          <t xml:space="preserve">...111...</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t xml:space="preserve">25555554.</t>
+          <t xml:space="preserve">...111...</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t xml:space="preserve">15G55G54.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t xml:space="preserve">15555554.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t xml:space="preserve">.4444444.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t xml:space="preserve">.4333..4.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">.3....33.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">..33331..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t xml:space="preserve">...111...</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
     </row>
@@ -510,12 +510,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">箭頭</t>
+          <t xml:space="preserve">硬磚</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">隨機</t>
+          <t xml:space="preserve">bomb,ball</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="Q5">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -560,52 +560,52 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">....2....</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t xml:space="preserve">...222...</t>
+          <t xml:space="preserve">..11211..</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t xml:space="preserve">..22222..</t>
+          <t xml:space="preserve">..11111..</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t xml:space="preserve">..12G21..</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111G111.</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t xml:space="preserve">111111111</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t xml:space="preserve">...112...</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">...333...</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">...111...</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t xml:space="preserve">...111...</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">條紋</t>
+          <t xml:space="preserve">油漆桶</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">隨機</t>
+          <t xml:space="preserve">bomb,ball</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="Q6">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -673,27 +673,27 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">223222222</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t xml:space="preserve">.........</t>
+          <t xml:space="preserve">..11111..</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t xml:space="preserve">112B11B11</t>
+          <t xml:space="preserve">.1111111.</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t xml:space="preserve">.........</t>
+          <t xml:space="preserve">...1B1...</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t xml:space="preserve">222222222</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t xml:space="preserve">111GBG111</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">545555.55</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t xml:space="preserve">444444444</t>
+          <t xml:space="preserve">.........</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">隨機</t>
+          <t xml:space="preserve">bomb,ball</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">隨機</t>
+          <t xml:space="preserve">bomb,ball</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">隨機</t>
+          <t xml:space="preserve">bomb,ball</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">隨機</t>
+          <t xml:space="preserve">bomb,ball</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
